--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/99.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/99.xlsx
@@ -426,13 +426,13 @@
         <v>-6.400168476585344</v>
       </c>
       <c r="E2">
-        <v>-12.48544417783352</v>
+        <v>-8.930854733304736</v>
       </c>
       <c r="F2">
-        <v>2.788530925610536</v>
+        <v>2.524913573750148</v>
       </c>
       <c r="G2">
-        <v>-19.44459962358045</v>
+        <v>-20.83949633127959</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.800093276410401</v>
       </c>
       <c r="E3">
-        <v>-13.00235137191306</v>
+        <v>-10.07325287121974</v>
       </c>
       <c r="F3">
-        <v>2.940680720318635</v>
+        <v>2.57272723904318</v>
       </c>
       <c r="G3">
-        <v>-19.17631797889622</v>
+        <v>-20.08682559492582</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.077335423683183</v>
       </c>
       <c r="E4">
-        <v>-13.42461345923229</v>
+        <v>-10.55167256470809</v>
       </c>
       <c r="F4">
-        <v>2.800052386145358</v>
+        <v>3.079202725624377</v>
       </c>
       <c r="G4">
-        <v>-17.84346751569409</v>
+        <v>-19.20714577895791</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.310008709746662</v>
       </c>
       <c r="E5">
-        <v>-12.45631703301619</v>
+        <v>-11.69046150883898</v>
       </c>
       <c r="F5">
-        <v>3.329624639797324</v>
+        <v>2.932420110263703</v>
       </c>
       <c r="G5">
-        <v>-17.88847603757326</v>
+        <v>-19.25997877521914</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.495480191197384</v>
       </c>
       <c r="E6">
-        <v>-14.75256129113758</v>
+        <v>-13.65310667223732</v>
       </c>
       <c r="F6">
-        <v>3.433313033492976</v>
+        <v>2.86598998193468</v>
       </c>
       <c r="G6">
-        <v>-17.53785615950904</v>
+        <v>-17.66941889451245</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.66168653165719</v>
       </c>
       <c r="E7">
-        <v>-14.37172568404052</v>
+        <v>-13.40197561766795</v>
       </c>
       <c r="F7">
-        <v>3.220347347926087</v>
+        <v>2.974958451152406</v>
       </c>
       <c r="G7">
-        <v>-16.3374424153327</v>
+        <v>-17.75285291846593</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.824739943681742</v>
       </c>
       <c r="E8">
-        <v>-15.91809993123178</v>
+        <v>-15.02042505716529</v>
       </c>
       <c r="F8">
-        <v>3.790530572367667</v>
+        <v>3.440834052885398</v>
       </c>
       <c r="G8">
-        <v>-15.66598598214832</v>
+        <v>-15.81358334447119</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.00414139162017</v>
       </c>
       <c r="E9">
-        <v>-16.23689544442375</v>
+        <v>-14.30002182660306</v>
       </c>
       <c r="F9">
-        <v>3.768041948368426</v>
+        <v>3.592964843122511</v>
       </c>
       <c r="G9">
-        <v>-15.12810675092801</v>
+        <v>-15.53832141451741</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.2024015072828423</v>
       </c>
       <c r="E10">
-        <v>-18.21919871348939</v>
+        <v>-14.51661873838994</v>
       </c>
       <c r="F10">
-        <v>3.490636852808222</v>
+        <v>3.734906069499687</v>
       </c>
       <c r="G10">
-        <v>-13.67858935237643</v>
+        <v>-15.22965608007238</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.5698868078081625</v>
       </c>
       <c r="E11">
-        <v>-17.77798496244806</v>
+        <v>-16.31595807212367</v>
       </c>
       <c r="F11">
-        <v>3.927198058046429</v>
+        <v>3.720800000910867</v>
       </c>
       <c r="G11">
-        <v>-13.01954580969156</v>
+        <v>-14.89673106791557</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.3089597970184</v>
       </c>
       <c r="E12">
-        <v>-18.32450837653776</v>
+        <v>-16.86303396004231</v>
       </c>
       <c r="F12">
-        <v>3.950302743646775</v>
+        <v>3.886067631716551</v>
       </c>
       <c r="G12">
-        <v>-12.19340248091197</v>
+        <v>-12.85965308123584</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.021273048559277</v>
       </c>
       <c r="E13">
-        <v>-18.90804300869216</v>
+        <v>-16.02599535293853</v>
       </c>
       <c r="F13">
-        <v>4.086840365440471</v>
+        <v>3.701572227391517</v>
       </c>
       <c r="G13">
-        <v>-12.01227260282183</v>
+        <v>-12.42158183220624</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.706897330123768</v>
       </c>
       <c r="E14">
-        <v>-18.9612616352303</v>
+        <v>-17.90809707763644</v>
       </c>
       <c r="F14">
-        <v>4.217825514294637</v>
+        <v>3.719848193655689</v>
       </c>
       <c r="G14">
-        <v>-11.648450269147</v>
+        <v>-11.74101312242502</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.364850990735823</v>
       </c>
       <c r="E15">
-        <v>-20.19474097086158</v>
+        <v>-19.37787671546197</v>
       </c>
       <c r="F15">
-        <v>4.306978655098385</v>
+        <v>3.796170149132546</v>
       </c>
       <c r="G15">
-        <v>-11.06632394152155</v>
+        <v>-11.67787439790004</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.995830267938656</v>
       </c>
       <c r="E16">
-        <v>-21.54050381951304</v>
+        <v>-19.80738888966748</v>
       </c>
       <c r="F16">
-        <v>4.824674698090472</v>
+        <v>3.906988386859506</v>
       </c>
       <c r="G16">
-        <v>-10.77833958506035</v>
+        <v>-10.38572543683049</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.587184105822332</v>
       </c>
       <c r="E17">
-        <v>-21.82472443365645</v>
+        <v>-20.27672446429644</v>
       </c>
       <c r="F17">
-        <v>5.0294589588982</v>
+        <v>4.177700741221064</v>
       </c>
       <c r="G17">
-        <v>-9.975760719429301</v>
+        <v>-10.77809460469045</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.117875067757899</v>
       </c>
       <c r="E18">
-        <v>-22.76251253048288</v>
+        <v>-21.7743904450612</v>
       </c>
       <c r="F18">
-        <v>5.081632566576437</v>
+        <v>4.670909523348624</v>
       </c>
       <c r="G18">
-        <v>-9.785818169113616</v>
+        <v>-10.95126924184972</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.566394017130985</v>
       </c>
       <c r="E19">
-        <v>-23.66364715869123</v>
+        <v>-21.82966952727283</v>
       </c>
       <c r="F19">
-        <v>5.402035277740822</v>
+        <v>4.990189387018964</v>
       </c>
       <c r="G19">
-        <v>-9.557228310172482</v>
+        <v>-9.698621710154754</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.90950831976659</v>
       </c>
       <c r="E20">
-        <v>-24.06430389651987</v>
+        <v>-22.0554773551913</v>
       </c>
       <c r="F20">
-        <v>5.199029518676133</v>
+        <v>4.996180546497071</v>
       </c>
       <c r="G20">
-        <v>-9.390492684087087</v>
+        <v>-9.77136101674362</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.127465051888451</v>
       </c>
       <c r="E21">
-        <v>-24.64055674246993</v>
+        <v>-22.16077796129166</v>
       </c>
       <c r="F21">
-        <v>5.583475713354973</v>
+        <v>4.593396621023356</v>
       </c>
       <c r="G21">
-        <v>-9.406350197220197</v>
+        <v>-10.45959363944825</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.211124400239678</v>
       </c>
       <c r="E22">
-        <v>-24.65119865638795</v>
+        <v>-24.18728819362018</v>
       </c>
       <c r="F22">
-        <v>5.75354514049627</v>
+        <v>4.839206783570543</v>
       </c>
       <c r="G22">
-        <v>-9.460914608798465</v>
+        <v>-9.44921514086268</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.162273649262854</v>
       </c>
       <c r="E23">
-        <v>-24.91906695088967</v>
+        <v>-23.23950122618481</v>
       </c>
       <c r="F23">
-        <v>5.492973255111271</v>
+        <v>4.873362569048826</v>
       </c>
       <c r="G23">
-        <v>-8.888302789052885</v>
+        <v>-9.799371542551393</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.995175794337603</v>
       </c>
       <c r="E24">
-        <v>-24.84462789515158</v>
+        <v>-24.80502638995451</v>
       </c>
       <c r="F24">
-        <v>5.214904586772497</v>
+        <v>5.006373277768839</v>
       </c>
       <c r="G24">
-        <v>-9.006644860445212</v>
+        <v>-9.510145731512965</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.73560454511664</v>
       </c>
       <c r="E25">
-        <v>-25.90182732308627</v>
+        <v>-25.09407888586411</v>
       </c>
       <c r="F25">
-        <v>5.04549873240977</v>
+        <v>4.627203991200242</v>
       </c>
       <c r="G25">
-        <v>-9.027670135165122</v>
+        <v>-9.115949142515328</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.413636345875149</v>
       </c>
       <c r="E26">
-        <v>-25.88563350003485</v>
+        <v>-25.74985626386286</v>
       </c>
       <c r="F26">
-        <v>5.033823652401151</v>
+        <v>4.375358325409315</v>
       </c>
       <c r="G26">
-        <v>-8.423207556786215</v>
+        <v>-8.295761485160892</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.057884667462495</v>
       </c>
       <c r="E27">
-        <v>-25.44584168983192</v>
+        <v>-24.68167981493358</v>
       </c>
       <c r="F27">
-        <v>5.068823553132363</v>
+        <v>4.181031274761232</v>
       </c>
       <c r="G27">
-        <v>-8.327039519415926</v>
+        <v>-9.148177303340134</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.689136962691339</v>
       </c>
       <c r="E28">
-        <v>-26.68926102591004</v>
+        <v>-23.57209952815217</v>
       </c>
       <c r="F28">
-        <v>5.106218017207719</v>
+        <v>4.26336814530493</v>
       </c>
       <c r="G28">
-        <v>-8.334749779976889</v>
+        <v>-9.390896570642878</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.31664121485254</v>
       </c>
       <c r="E29">
-        <v>-26.0058101432504</v>
+        <v>-24.72957748451271</v>
       </c>
       <c r="F29">
-        <v>4.902358640654607</v>
+        <v>4.379080034310597</v>
       </c>
       <c r="G29">
-        <v>-8.255760163409878</v>
+        <v>-8.533710256341548</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.942510431879561</v>
       </c>
       <c r="E30">
-        <v>-25.13403361203378</v>
+        <v>-24.58409572854229</v>
       </c>
       <c r="F30">
-        <v>4.804221136192571</v>
+        <v>4.225303773627343</v>
       </c>
       <c r="G30">
-        <v>-7.887541425258901</v>
+        <v>-8.166458197488037</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.560505846777867</v>
       </c>
       <c r="E31">
-        <v>-25.01671443591707</v>
+        <v>-23.96723152769145</v>
       </c>
       <c r="F31">
-        <v>4.781759435193893</v>
+        <v>4.171657319447746</v>
       </c>
       <c r="G31">
-        <v>-7.962048563165738</v>
+        <v>-8.310817846273498</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.159304744856548</v>
       </c>
       <c r="E32">
-        <v>-25.00509437161338</v>
+        <v>-24.69498900004212</v>
       </c>
       <c r="F32">
-        <v>4.955746950769986</v>
+        <v>3.95558281916885</v>
       </c>
       <c r="G32">
-        <v>-8.222416348738339</v>
+        <v>-7.680437006867635</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.736053936381557</v>
       </c>
       <c r="E33">
-        <v>-24.96466868414691</v>
+        <v>-24.03912105256321</v>
       </c>
       <c r="F33">
-        <v>4.696620988885784</v>
+        <v>3.846742630130274</v>
       </c>
       <c r="G33">
-        <v>-7.706226156618557</v>
+        <v>-8.608217394248385</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.290327202169502</v>
       </c>
       <c r="E34">
-        <v>-24.49858908232946</v>
+        <v>-22.67408501853511</v>
       </c>
       <c r="F34">
-        <v>4.551143347199432</v>
+        <v>4.130587073942656</v>
       </c>
       <c r="G34">
-        <v>-8.240299915741481</v>
+        <v>-8.250685097098176</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.822938180096665</v>
       </c>
       <c r="E35">
-        <v>-24.61850307405257</v>
+        <v>-22.84850372341453</v>
       </c>
       <c r="F35">
-        <v>4.756618103786292</v>
+        <v>4.279870360943809</v>
       </c>
       <c r="G35">
-        <v>-8.2824597131841</v>
+        <v>-8.049059631574403</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.347816566169685</v>
       </c>
       <c r="E36">
-        <v>-21.99834612711053</v>
+        <v>-22.28973078713408</v>
       </c>
       <c r="F36">
-        <v>4.83431154858592</v>
+        <v>4.550544706363396</v>
       </c>
       <c r="G36">
-        <v>-8.653651321229342</v>
+        <v>-7.487610971387245</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.8837952094731621</v>
       </c>
       <c r="E37">
-        <v>-22.87499529635941</v>
+        <v>-22.64330498070497</v>
       </c>
       <c r="F37">
-        <v>4.689101553199277</v>
+        <v>4.457212165648802</v>
       </c>
       <c r="G37">
-        <v>-8.392502246909475</v>
+        <v>-8.755715440205073</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.445618525976238</v>
       </c>
       <c r="E38">
-        <v>-23.0613782295671</v>
+        <v>-21.74266848463747</v>
       </c>
       <c r="F38">
-        <v>4.935478682464193</v>
+        <v>4.344521987529793</v>
       </c>
       <c r="G38">
-        <v>-8.441110987062594</v>
+        <v>-8.34754834903171</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.04635254511864791</v>
       </c>
       <c r="E39">
-        <v>-21.25778665874017</v>
+        <v>-20.4398265126307</v>
       </c>
       <c r="F39">
-        <v>4.927382777824466</v>
+        <v>4.81050686497095</v>
       </c>
       <c r="G39">
-        <v>-8.693010397145738</v>
+        <v>-8.848864260043547</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.3071388427646706</v>
       </c>
       <c r="E40">
-        <v>-21.49758294286834</v>
+        <v>-20.76546002157426</v>
       </c>
       <c r="F40">
-        <v>4.952220037696303</v>
+        <v>4.48846660189</v>
       </c>
       <c r="G40">
-        <v>-8.62708750382223</v>
+        <v>-9.577909288156308</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.6179948528271059</v>
       </c>
       <c r="E41">
-        <v>-20.75648005761705</v>
+        <v>-20.66280857276839</v>
       </c>
       <c r="F41">
-        <v>5.002372836626439</v>
+        <v>4.815921555495837</v>
       </c>
       <c r="G41">
-        <v>-8.642931774773182</v>
+        <v>-10.04165050729742</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8930453695504215</v>
       </c>
       <c r="E42">
-        <v>-21.0692934566449</v>
+        <v>-19.30139531794642</v>
       </c>
       <c r="F42">
-        <v>5.003790253420758</v>
+        <v>4.800931779006203</v>
       </c>
       <c r="G42">
-        <v>-8.73070095811034</v>
+        <v>-9.127645299905573</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.138751537285466</v>
       </c>
       <c r="E43">
-        <v>-20.24228541946811</v>
+        <v>-20.7458788999651</v>
       </c>
       <c r="F43">
-        <v>4.973295996018971</v>
+        <v>5.132578802170209</v>
       </c>
       <c r="G43">
-        <v>-9.156781411196699</v>
+        <v>-9.700200840376986</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.362719405030553</v>
       </c>
       <c r="E44">
-        <v>-20.64065527792287</v>
+        <v>-18.26937420549438</v>
       </c>
       <c r="F44">
-        <v>4.738087160869735</v>
+        <v>4.498591233807405</v>
       </c>
       <c r="G44">
-        <v>-9.57085782615766</v>
+        <v>-9.598308869769298</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.57033729400088</v>
       </c>
       <c r="E45">
-        <v>-19.35506679188533</v>
+        <v>-19.40035153196203</v>
       </c>
       <c r="F45">
-        <v>4.959904178798014</v>
+        <v>4.560970242404734</v>
       </c>
       <c r="G45">
-        <v>-9.540311422466806</v>
+        <v>-9.871144169842793</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.762735767392243</v>
       </c>
       <c r="E46">
-        <v>-19.02127297277995</v>
+        <v>-17.70856798438448</v>
       </c>
       <c r="F46">
-        <v>4.65055098380565</v>
+        <v>4.814508889819265</v>
       </c>
       <c r="G46">
-        <v>-9.858478022609541</v>
+        <v>-9.491169684481864</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.940899648539653</v>
       </c>
       <c r="E47">
-        <v>-19.42491397497964</v>
+        <v>-18.75413376259347</v>
       </c>
       <c r="F47">
-        <v>4.983829224062559</v>
+        <v>4.674246391712455</v>
       </c>
       <c r="G47">
-        <v>-9.855339625438312</v>
+        <v>-10.30628558607014</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.105588351380806</v>
       </c>
       <c r="E48">
-        <v>-18.44934481950721</v>
+        <v>-17.21153626272461</v>
       </c>
       <c r="F48">
-        <v>4.843107451240271</v>
+        <v>4.840258364298395</v>
       </c>
       <c r="G48">
-        <v>-10.86636699094958</v>
+        <v>-11.27322972718047</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.255191935366978</v>
       </c>
       <c r="E49">
-        <v>-17.91516602556242</v>
+        <v>-16.82285733864626</v>
       </c>
       <c r="F49">
-        <v>5.123548511040373</v>
+        <v>4.787682495317637</v>
       </c>
       <c r="G49">
-        <v>-9.914257404400722</v>
+        <v>-11.24059105870879</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.389078041025397</v>
       </c>
       <c r="E50">
-        <v>-18.85146878291433</v>
+        <v>-17.27968526806604</v>
       </c>
       <c r="F50">
-        <v>4.905297998833663</v>
+        <v>4.705431144893374</v>
       </c>
       <c r="G50">
-        <v>-10.51563455433703</v>
+        <v>-11.18547378602547</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.508747673739597</v>
       </c>
       <c r="E51">
-        <v>-17.18552470802455</v>
+        <v>-16.55210440620166</v>
       </c>
       <c r="F51">
-        <v>4.705695623781252</v>
+        <v>4.563070236448606</v>
       </c>
       <c r="G51">
-        <v>-10.00935944610736</v>
+        <v>-10.74297302706432</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.614567006851665</v>
       </c>
       <c r="E52">
-        <v>-16.20076727879056</v>
+        <v>-16.30186093253779</v>
       </c>
       <c r="F52">
-        <v>4.568271126674909</v>
+        <v>4.68630156114078</v>
       </c>
       <c r="G52">
-        <v>-9.872779579339193</v>
+        <v>-10.23823732251042</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.706664809161226</v>
       </c>
       <c r="E53">
-        <v>-16.29799814420925</v>
+        <v>-15.88113399790716</v>
       </c>
       <c r="F53">
-        <v>4.91539729145642</v>
+        <v>4.684570570575205</v>
       </c>
       <c r="G53">
-        <v>-10.25854089830277</v>
+        <v>-10.82884857835302</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.786969614665473</v>
       </c>
       <c r="E54">
-        <v>-16.23217224603375</v>
+        <v>-16.23649693871108</v>
       </c>
       <c r="F54">
-        <v>4.981760904136994</v>
+        <v>4.435163811894054</v>
       </c>
       <c r="G54">
-        <v>-10.57300961907814</v>
+        <v>-10.80707180979569</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.857194978732059</v>
       </c>
       <c r="E55">
-        <v>-16.44753741289054</v>
+        <v>-13.65222361980582</v>
       </c>
       <c r="F55">
-        <v>4.831885311123467</v>
+        <v>4.561043092876844</v>
       </c>
       <c r="G55">
-        <v>-10.54118534480912</v>
+        <v>-11.8287160948514</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.918976556337721</v>
       </c>
       <c r="E56">
-        <v>-15.21922053762801</v>
+        <v>-14.63766484861497</v>
       </c>
       <c r="F56">
-        <v>4.639746942050523</v>
+        <v>4.658073586903988</v>
       </c>
       <c r="G56">
-        <v>-11.1704041827307</v>
+        <v>-10.46109993766861</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.97526296722326</v>
       </c>
       <c r="E57">
-        <v>-14.99981144348237</v>
+        <v>-14.00468380877082</v>
       </c>
       <c r="F57">
-        <v>4.64608176571228</v>
+        <v>4.427588946500507</v>
       </c>
       <c r="G57">
-        <v>-11.06256316178894</v>
+        <v>-10.743873495451</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.028326075399476</v>
       </c>
       <c r="E58">
-        <v>-15.47156975170544</v>
+        <v>-14.67741126498029</v>
       </c>
       <c r="F58">
-        <v>4.543959657166998</v>
+        <v>4.611808785996255</v>
       </c>
       <c r="G58">
-        <v>-10.96929847285659</v>
+        <v>-12.53851030065329</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.078701155039362</v>
       </c>
       <c r="E59">
-        <v>-14.89861816330697</v>
+        <v>-13.48439837308156</v>
       </c>
       <c r="F59">
-        <v>4.864037708618719</v>
+        <v>4.533439098770734</v>
       </c>
       <c r="G59">
-        <v>-10.57044725683074</v>
+        <v>-11.88438622863978</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.125614346066804</v>
       </c>
       <c r="E60">
-        <v>-13.83498377380738</v>
+        <v>-12.42194138682396</v>
       </c>
       <c r="F60">
-        <v>4.910145722640823</v>
+        <v>4.296079590988332</v>
       </c>
       <c r="G60">
-        <v>-10.59822935499631</v>
+        <v>-12.31874635611986</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.166167425797526</v>
       </c>
       <c r="E61">
-        <v>-14.42508016479889</v>
+        <v>-11.71808972875977</v>
       </c>
       <c r="F61">
-        <v>4.863277529779308</v>
+        <v>4.289923726095018</v>
       </c>
       <c r="G61">
-        <v>-11.60846550012368</v>
+        <v>-12.01333197739439</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.196441789679155</v>
       </c>
       <c r="E62">
-        <v>-14.6803728869813</v>
+        <v>-12.96667152520663</v>
       </c>
       <c r="F62">
-        <v>4.439460406042642</v>
+        <v>4.543519386922506</v>
       </c>
       <c r="G62">
-        <v>-10.70757998470397</v>
+        <v>-12.16259123357797</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.213145935359257</v>
       </c>
       <c r="E63">
-        <v>-14.11753790951597</v>
+        <v>-13.69573319807152</v>
       </c>
       <c r="F63">
-        <v>4.50264552095093</v>
+        <v>3.671865071829704</v>
       </c>
       <c r="G63">
-        <v>-10.95000130290818</v>
+        <v>-13.03558209228379</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.213753152757377</v>
       </c>
       <c r="E64">
-        <v>-13.63087639333366</v>
+        <v>-13.1598879256919</v>
       </c>
       <c r="F64">
-        <v>4.392864610598583</v>
+        <v>4.614350633990536</v>
       </c>
       <c r="G64">
-        <v>-11.16500468295615</v>
+        <v>-12.44856608889684</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.196989100301228</v>
       </c>
       <c r="E65">
-        <v>-13.41423419680671</v>
+        <v>-12.65986288271295</v>
       </c>
       <c r="F65">
-        <v>4.765029165903191</v>
+        <v>4.332089896093594</v>
       </c>
       <c r="G65">
-        <v>-11.58001467175919</v>
+        <v>-12.98038536650752</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.162742198421479</v>
       </c>
       <c r="E66">
-        <v>-13.6063411211601</v>
+        <v>-12.40257310349315</v>
       </c>
       <c r="F66">
-        <v>4.331008224953348</v>
+        <v>4.444729395623309</v>
       </c>
       <c r="G66">
-        <v>-10.86302333995491</v>
+        <v>-11.8285307043012</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.111983797599664</v>
       </c>
       <c r="E67">
-        <v>-14.03231655716562</v>
+        <v>-11.95472060955658</v>
       </c>
       <c r="F67">
-        <v>4.169761623466965</v>
+        <v>4.362866053148329</v>
       </c>
       <c r="G67">
-        <v>-11.57833291462524</v>
+        <v>-12.33240235646935</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.046406978524467</v>
       </c>
       <c r="E68">
-        <v>-14.28858290125969</v>
+        <v>-11.96734146661596</v>
       </c>
       <c r="F68">
-        <v>4.265925830358364</v>
+        <v>4.10047765707832</v>
       </c>
       <c r="G68">
-        <v>-11.62633913549021</v>
+        <v>-11.69221568117617</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.966326972668024</v>
       </c>
       <c r="E69">
-        <v>-15.11239383578707</v>
+        <v>-12.40491885302913</v>
       </c>
       <c r="F69">
-        <v>4.196936433269991</v>
+        <v>4.177604135160221</v>
       </c>
       <c r="G69">
-        <v>-11.59764332675581</v>
+        <v>-12.45977890663835</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.870624167538177</v>
       </c>
       <c r="E70">
-        <v>-13.97166670478089</v>
+        <v>-11.68481450175141</v>
       </c>
       <c r="F70">
-        <v>4.24032364052937</v>
+        <v>3.535154826091225</v>
       </c>
       <c r="G70">
-        <v>-11.16006203846602</v>
+        <v>-12.9434694731991</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.758493707981057</v>
       </c>
       <c r="E71">
-        <v>-14.05286677221243</v>
+        <v>-12.84818853126994</v>
       </c>
       <c r="F71">
-        <v>4.382624368149351</v>
+        <v>3.914145153891377</v>
       </c>
       <c r="G71">
-        <v>-11.59331975428152</v>
+        <v>-12.28550185781449</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.626957345025046</v>
       </c>
       <c r="E72">
-        <v>-14.63136121279629</v>
+        <v>-13.45201525545271</v>
       </c>
       <c r="F72">
-        <v>4.326402808151251</v>
+        <v>4.155555781405474</v>
       </c>
       <c r="G72">
-        <v>-11.37015587947925</v>
+        <v>-11.8158777992501</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.470648934393221</v>
       </c>
       <c r="E73">
-        <v>-14.63137932669232</v>
+        <v>-12.90658320359885</v>
       </c>
       <c r="F73">
-        <v>3.991786336395796</v>
+        <v>4.08334037536735</v>
       </c>
       <c r="G73">
-        <v>-10.76889790918235</v>
+        <v>-12.54851145872743</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.286813151577231</v>
       </c>
       <c r="E74">
-        <v>-14.06507553813711</v>
+        <v>-12.63625594771097</v>
       </c>
       <c r="F74">
-        <v>3.819989086100755</v>
+        <v>3.646871025072239</v>
       </c>
       <c r="G74">
-        <v>-11.04244828709233</v>
+        <v>-12.57985239334771</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.073167173184463</v>
       </c>
       <c r="E75">
-        <v>-14.79915023172849</v>
+        <v>-13.77059793036632</v>
       </c>
       <c r="F75">
-        <v>3.998691294187112</v>
+        <v>3.670569600390875</v>
       </c>
       <c r="G75">
-        <v>-10.68866683803812</v>
+        <v>-12.52497347994322</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.826085955504098</v>
       </c>
       <c r="E76">
-        <v>-15.05527166465431</v>
+        <v>-13.0317773960149</v>
       </c>
       <c r="F76">
-        <v>3.874737799597497</v>
+        <v>3.70269982600331</v>
       </c>
       <c r="G76">
-        <v>-10.88691223656629</v>
+        <v>-12.06806191624962</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.545778093080973</v>
       </c>
       <c r="E77">
-        <v>-15.69397216717015</v>
+        <v>-14.14638428894483</v>
       </c>
       <c r="F77">
-        <v>3.876050691801396</v>
+        <v>3.61170325151399</v>
       </c>
       <c r="G77">
-        <v>-11.29548983538652</v>
+        <v>-11.56614679649518</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.234068017836233</v>
       </c>
       <c r="E78">
-        <v>-16.35214963639297</v>
+        <v>-15.08837480965038</v>
       </c>
       <c r="F78">
-        <v>3.592553079584496</v>
+        <v>3.055774964017281</v>
       </c>
       <c r="G78">
-        <v>-11.26108995668796</v>
+        <v>-12.14406211019467</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.8907952534072309</v>
       </c>
       <c r="E79">
-        <v>-17.21078906451334</v>
+        <v>-14.75295526837625</v>
       </c>
       <c r="F79">
-        <v>4.029906137780423</v>
+        <v>3.690232893036971</v>
       </c>
       <c r="G79">
-        <v>-10.07480562087322</v>
+        <v>-11.47501409889012</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5185045567349955</v>
       </c>
       <c r="E80">
-        <v>-17.33206159843875</v>
+        <v>-14.80875965357277</v>
       </c>
       <c r="F80">
-        <v>3.532650987038915</v>
+        <v>3.372281758629685</v>
       </c>
       <c r="G80">
-        <v>-10.49756228623815</v>
+        <v>-10.48290981168133</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.1221374660758347</v>
       </c>
       <c r="E81">
-        <v>-17.51516591646489</v>
+        <v>-16.44623774085034</v>
       </c>
       <c r="F81">
-        <v>3.555800016404893</v>
+        <v>3.270536572092278</v>
       </c>
       <c r="G81">
-        <v>-10.14251620878793</v>
+        <v>-10.6629538308346</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.2949752992936379</v>
       </c>
       <c r="E82">
-        <v>-18.2241030508397</v>
+        <v>-17.06538882107506</v>
       </c>
       <c r="F82">
-        <v>3.197971167046843</v>
+        <v>3.299595991934677</v>
       </c>
       <c r="G82">
-        <v>-9.844030801876162</v>
+        <v>-10.43787977125617</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.7269606096548485</v>
       </c>
       <c r="E83">
-        <v>-19.02719168830797</v>
+        <v>-16.31771059156464</v>
       </c>
       <c r="F83">
-        <v>3.455933105083197</v>
+        <v>3.051004841799978</v>
       </c>
       <c r="G83">
-        <v>-9.898419754540848</v>
+        <v>-9.794985069711858</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.163792584214886</v>
       </c>
       <c r="E84">
-        <v>-19.3903526613531</v>
+        <v>-18.53551262292516</v>
       </c>
       <c r="F84">
-        <v>3.577804026394009</v>
+        <v>3.310450712279099</v>
       </c>
       <c r="G84">
-        <v>-8.838876344151565</v>
+        <v>-9.555364473033871</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.595583278845437</v>
       </c>
       <c r="E85">
-        <v>-20.16611195818508</v>
+        <v>-19.08259756779182</v>
       </c>
       <c r="F85">
-        <v>3.299755946232136</v>
+        <v>2.914931245839505</v>
       </c>
       <c r="G85">
-        <v>-9.381560832222133</v>
+        <v>-11.19679254122423</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.010897643342321</v>
       </c>
       <c r="E86">
-        <v>-22.84274803295079</v>
+        <v>-19.92439560107766</v>
       </c>
       <c r="F86">
-        <v>3.262035238738199</v>
+        <v>3.028170969911172</v>
       </c>
       <c r="G86">
-        <v>-9.051956297241215</v>
+        <v>-9.659130212416787</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.395030485983909</v>
       </c>
       <c r="E87">
-        <v>-23.63592384081627</v>
+        <v>-20.63437428447423</v>
       </c>
       <c r="F87">
-        <v>3.162852488371973</v>
+        <v>2.597298436321223</v>
       </c>
       <c r="G87">
-        <v>-8.375356931561589</v>
+        <v>-9.072137382848613</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.734636233293428</v>
       </c>
       <c r="E88">
-        <v>-24.9986684669965</v>
+        <v>-22.71709193618595</v>
       </c>
       <c r="F88">
-        <v>2.932021016373012</v>
+        <v>2.682539823513836</v>
       </c>
       <c r="G88">
-        <v>-8.313426556158442</v>
+        <v>-8.551944741171853</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.018067148338233</v>
       </c>
       <c r="E89">
-        <v>-26.3515998900021</v>
+        <v>-24.96124515779711</v>
       </c>
       <c r="F89">
-        <v>3.237772864113667</v>
+        <v>2.755068803323216</v>
       </c>
       <c r="G89">
-        <v>-8.165279643276056</v>
+        <v>-8.085988767064972</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.2332694052693</v>
       </c>
       <c r="E90">
-        <v>-26.29221348186551</v>
+        <v>-24.9372125462384</v>
       </c>
       <c r="F90">
-        <v>3.308171759466781</v>
+        <v>2.820003913268064</v>
       </c>
       <c r="G90">
-        <v>-7.420052668567338</v>
+        <v>-7.130264064787235</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.3708895415505</v>
       </c>
       <c r="E91">
-        <v>-29.00553472456735</v>
+        <v>-26.95179930650472</v>
       </c>
       <c r="F91">
-        <v>3.008670798974366</v>
+        <v>2.363793668737</v>
       </c>
       <c r="G91">
-        <v>-8.046950814065887</v>
+        <v>-7.980554512730264</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.425514819227931</v>
       </c>
       <c r="E92">
-        <v>-29.11332599137193</v>
+        <v>-27.7488062033807</v>
       </c>
       <c r="F92">
-        <v>2.682829641696361</v>
+        <v>2.458390006772114</v>
       </c>
       <c r="G92">
-        <v>-7.010978487916215</v>
+        <v>-7.128340637828918</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.395106185335935</v>
       </c>
       <c r="E93">
-        <v>-32.51907355221661</v>
+        <v>-32.0784643524553</v>
       </c>
       <c r="F93">
-        <v>2.922783259768253</v>
+        <v>2.328280647289186</v>
       </c>
       <c r="G93">
-        <v>-7.31411521131066</v>
+        <v>-7.947008754780829</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.282913030264066</v>
       </c>
       <c r="E94">
-        <v>-34.66393771697259</v>
+        <v>-34.9035800329845</v>
       </c>
       <c r="F94">
-        <v>2.507315433617785</v>
+        <v>2.206264025034153</v>
       </c>
       <c r="G94">
-        <v>-7.545158184496396</v>
+        <v>-8.165223364001889</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.099680782689378</v>
       </c>
       <c r="E95">
-        <v>-36.03525700868634</v>
+        <v>-36.07660876908739</v>
       </c>
       <c r="F95">
-        <v>2.356355002052181</v>
+        <v>2.457438199516934</v>
       </c>
       <c r="G95">
-        <v>-7.002284995330089</v>
+        <v>-7.531882896883919</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.859774450648598</v>
       </c>
       <c r="E96">
-        <v>-38.21832338017104</v>
+        <v>-37.87900255853929</v>
       </c>
       <c r="F96">
-        <v>2.86116284630442</v>
+        <v>2.182904362781422</v>
       </c>
       <c r="G96">
-        <v>-6.594276810342611</v>
+        <v>-7.148614418711414</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.58574454327785</v>
       </c>
       <c r="E97">
-        <v>-40.37780093054977</v>
+        <v>-39.18184226630905</v>
       </c>
       <c r="F97">
-        <v>2.094665020290882</v>
+        <v>2.229736130406882</v>
       </c>
       <c r="G97">
-        <v>-6.844514326565042</v>
+        <v>-8.009041757095693</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.295149586572023</v>
       </c>
       <c r="E98">
-        <v>-42.70964578708247</v>
+        <v>-43.41141887557713</v>
       </c>
       <c r="F98">
-        <v>2.090952813625092</v>
+        <v>1.832390651046786</v>
       </c>
       <c r="G98">
-        <v>-7.25987854374078</v>
+        <v>-7.842716638657169</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.017275586580099</v>
       </c>
       <c r="E99">
-        <v>-44.2504590681923</v>
+        <v>-45.06893546033864</v>
       </c>
       <c r="F99">
-        <v>1.744331851030606</v>
+        <v>1.126041975701638</v>
       </c>
       <c r="G99">
-        <v>-7.426319531273178</v>
+        <v>-7.531800133245437</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.758931114011678</v>
       </c>
       <c r="E100">
-        <v>-46.93814688377373</v>
+        <v>-47.16585667077542</v>
       </c>
       <c r="F100">
-        <v>1.921391756082652</v>
+        <v>1.832530017167345</v>
       </c>
       <c r="G100">
-        <v>-7.596491503628335</v>
+        <v>-8.786556482448923</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.550926321495698</v>
       </c>
       <c r="E101">
-        <v>-49.50998614517242</v>
+        <v>-47.40019387948734</v>
       </c>
       <c r="F101">
-        <v>1.670919163320411</v>
+        <v>1.34202778844927</v>
       </c>
       <c r="G101">
-        <v>-7.824141167636318</v>
+        <v>-7.68609141864871</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.368074867151924</v>
       </c>
       <c r="E102">
-        <v>-51.42499515836558</v>
+        <v>-51.24387204771779</v>
       </c>
       <c r="F102">
-        <v>1.747041571851923</v>
+        <v>1.112133870352249</v>
       </c>
       <c r="G102">
-        <v>-8.221095441068169</v>
+        <v>-8.150200108344677</v>
       </c>
     </row>
   </sheetData>
